--- a/text/foundationScores/milkywaysynonyms_3_seconds_MFT_MAC.xlsx
+++ b/text/foundationScores/milkywaysynonyms_3_seconds_MFT_MAC.xlsx
@@ -425,166 +425,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG57"/>
+  <dimension ref="A1:AI57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>chunkEnd</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>chunkStart</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>V_neu</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>V_neg</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>V_pos</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>V_com</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sentence</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>full_text</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_care_virtue</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_fairness_virtue</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_loyalty_virtue</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_authority_virtue</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_sanctity_virtue</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_care_vice</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_fairness_vice</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_loyalty_vice</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_authority_vice</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_sanctity_vice</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_moral_nonmoral</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_fairness_virtue</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_group_virtue</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_deference_virtue</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_heroism_virtue</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_reciprocity_virtue</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_family_virtue</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_property_virtue</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_fairness_vice</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_group_vice</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_deference_vice</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_heroism_vice</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_reciprocity_vice</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_family_vice</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_property_vice</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_moral_nonmoral</t>
         </is>
@@ -594,104 +604,114 @@
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>24.358</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>21.175</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>79.60000000000001</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>20.4</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>31.82</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve"> Martin took a deep breath and tried to calm down.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>0.06751607525601333</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.04761904761904762</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>0.004219409282700422</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>0.1107561230909708</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>0.0916169084942699</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.04861111111111111</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>0.07517049669732478</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>0.05968377313690573</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>0.05967078189300411</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>0.05087719298245614</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.04824561403508772</v>
       </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
         <v>0.1279703934553954</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Z2" t="n">
         <v>0.03603603603603604</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AA2" t="n">
         <v>0.07034883720930232</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AB2" t="n">
         <v>0.09261287574540587</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AC2" t="n">
         <v>0.1467864923747277</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AD2" t="n">
         <v>0.1558730158730159</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AE2" t="n">
         <v>0.1587987355110643</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AF2" t="n">
         <v>0.03125</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AG2" t="n">
         <v>0.1006645114942529</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AH2" t="n">
         <v>0.05769230769230769</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AI2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -699,104 +719,114 @@
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>33.147</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>24.418</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>82.69999999999999</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>17.3</v>
       </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>-52.79000000000001</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve"> The situation was almost desperate, and after Martin spent most of the last weeks drunk, he knew it was time to face reality.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.006613756613756613</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>0.03835689135794703</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.01616832779623478</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
         <v>0.08077293456491862</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0.1169541782685074</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.04080275306362263</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>0.05932320648839124</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>0.0866642105261439</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>2.333333333333333</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0.06283166109253066</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>0.05016034020007668</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.008064516129032258</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>0.03562322106261859</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>0.09732759393776343</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>0.08416596161773664</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AA3" t="n">
         <v>0.03213276836158192</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AB3" t="n">
         <v>0.1066845491148751</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AC3" t="n">
         <v>0.1504762807009723</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AD3" t="n">
         <v>0.138026343378891</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AE3" t="n">
         <v>0.07986636179971827</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AF3" t="n">
         <v>0.0453050785531604</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AG3" t="n">
         <v>0.03678326721961774</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AH3" t="n">
         <v>0.06166069606891773</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AI3" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -804,73 +834,77 @@
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>38.151</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>34.308</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>35.09999999999999</v>
       </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>-65.97</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve"> Martin looked at the reflection in the mirror and started weeping uncontrollably.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.04320987654320987</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>0.05319148936170213</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.02873563218390804</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>0.03645833333333334</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>0.03626943005181347</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0.04373144553551039</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.03333333333333334</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>0.0456989247311828</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>0.02577319587628866</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>0.4</v>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>0.12</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
@@ -881,27 +915,33 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
         <v>0.1232876712328767</v>
       </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
         <v>0.09876543209876543</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AE4" t="n">
         <v>0.07339449541284404</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AF4" t="n">
         <v>0.1159420289855072</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AG4" t="n">
         <v>0.1232876712328767</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AH4" t="n">
         <v>0.180327868852459</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>0.1666666666666667</v>
       </c>
     </row>
@@ -909,104 +949,114 @@
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>46.9</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>39.773</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>79.60000000000001</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>20.4</v>
       </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>-62.49</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve"> That evening, at the utmost moment of hopelessness, Martin did the inconceivable, calling his mom to talk.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.015625</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>0.02427184466019417</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.02441860465116279</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.02606635071090047</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>0.01589595375722543</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>0.08798854306354409</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>0.03749194587628866</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0.07163446935180122</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>0.05130421118793212</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>0.08988095238095238</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>0.8</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>0.03070175438596491</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>0.03864734299516908</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.1200548374461418</v>
       </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0.05192348118562119</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>0.05389830508474577</v>
       </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
         <v>0.08854907539118066</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AC5" t="n">
         <v>0.09925925925925927</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AD5" t="n">
         <v>0.07792207792207792</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AE5" t="n">
         <v>0.1567422796478235</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AF5" t="n">
         <v>0.04477611940298507</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AG5" t="n">
         <v>0.01923076923076923</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AH5" t="n">
         <v>0.0803473886180653</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AI5" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1014,104 +1064,114 @@
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>64.951</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>48.261</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>73</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>22.2</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>4.8</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>-86.87</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">  In general...  Help from his mom resembled a lengthy and very excruciating lecture about all the things he had done wrong in his life, starting from how Martin struggled to remain in his mom's belly up to how Martin had messed up everything with Sophia Jones.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.0382219338092148</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>0.01773868991933349</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.04331519694771561</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.03995162342130516</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>0.03307262797644213</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>0.06836299140749033</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>0.04885146062999605</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.05145566549254765</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>0.0298150604185087</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>0.07431424829630159</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>0.09017422944911029</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>0.1171251703030978</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.04930146377617195</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>0.1020059978594212</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>0.1056966682330281</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>0.1214466914701519</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AA6" t="n">
         <v>0.02122914994202123</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AB6" t="n">
         <v>0.1391251363812339</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AC6" t="n">
         <v>0.05725268226746642</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AD6" t="n">
         <v>0.122693179836037</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AE6" t="n">
         <v>0.07672493841808638</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AF6" t="n">
         <v>0.1147566718995291</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AG6" t="n">
         <v>0.02804232804232804</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AH6" t="n">
         <v>0.0469760391973704</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>0.5384615384615384</v>
       </c>
     </row>
@@ -1119,104 +1179,114 @@
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>73.341</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>66.573</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>64.60000000000001</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>14.1</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>21.3</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>22.63</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">  To be honest, it wasn't far from the truth.  His mom had gone through nearly 30 hours of agonizing labor.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.03910189075630251</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>0.06035197311951916</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.03340024534403926</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.04144693473961767</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>0.04116896013618953</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>0.04021568846845106</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>0.03909426790757724</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.06191034103269999</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>0.02305650355414321</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>0.0447745863159397</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>3.5</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>0.0958100558659218</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.04462279293739968</v>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>0.06511627906976744</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>0.07538239538239538</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>0.08700066558436978</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
         <v>0.04017857142857143</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AB7" t="n">
         <v>0.1871816100878133</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AC7" t="n">
         <v>0.07846693657219973</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AD7" t="n">
         <v>0.05818429936076994</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AE7" t="n">
         <v>0.06686869652274988</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AF7" t="n">
         <v>0.04770887007729113</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AG7" t="n">
         <v>0.0032</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AH7" t="n">
         <v>0.0568222844693433</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AI7" t="n">
         <v>1.25</v>
       </c>
     </row>
@@ -1224,67 +1294,71 @@
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>78.267</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>73.701</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>81.10000000000001</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
         <v>18.9</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>42.15</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve"> Martin could imagine, though he never really tried, it could have gone easier.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>0.03472222222222222</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>0.04761904761904762</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>0.02272727272727272</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>0.1139548750180222</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0.07828945624221215</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.1034660921956004</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>0.01884920634920635</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>0.04888949079089924</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>1.5</v>
       </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
@@ -1292,36 +1366,42 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
         <v>0.2414438502673797</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
         <v>0.2087480356207438</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AC8" t="n">
         <v>0.1919444444444444</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AD8" t="n">
         <v>0.1980952380952381</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AE8" t="n">
         <v>0.1343519494204426</v>
       </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
         <v>0.06896551724137931</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AH8" t="n">
         <v>0.1436813186813187</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -1329,104 +1409,114 @@
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>87.05</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>79.462</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>71.39999999999999</v>
       </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>28.6</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>89.14</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve"> But to this day, each time Martin looked at his mom's belly, he felt that it was the only time he really felt protected and loved.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.050815962903322</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>0.04438581033194783</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.06280889147444396</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.03734428179689557</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>0.0327570055392636</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>0.04837612628289797</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>0.0220876479630431</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>0.04136064030131827</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>0.01804391650620598</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>0.05823870978392644</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>4.5</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>0.1812370600414079</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>0.1671733445121161</v>
       </c>
-      <c r="U9" t="n">
+      <c r="W9" t="n">
         <v>0.06480058086583049</v>
       </c>
-      <c r="V9" t="n">
+      <c r="X9" t="n">
         <v>0.07557562923301749</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
         <v>0.0369978723003634</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Z9" t="n">
         <v>0.1527300461536861</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AA9" t="n">
         <v>0.09741759364690082</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AB9" t="n">
         <v>0.04525156971340923</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AC9" t="n">
         <v>0.004464285714285714</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AD9" t="n">
         <v>0.02955665024630542</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AE9" t="n">
         <v>0.05935946468738777</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AF9" t="n">
         <v>0.1193126963664875</v>
       </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
         <v>0.02979842243645925</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AI9" t="n">
         <v>1.75</v>
       </c>
     </row>
@@ -1434,104 +1524,114 @@
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>93.037</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>88.952</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>100</v>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve"> As for Sophia, it wasn't that simple, as nothing in life ever is.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>0.0425531914893617</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>0.072744014732965</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>0.1211651368560324</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>0.1271335341365462</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>0.03614457831325301</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>0.09061587147030185</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>0.01162790697674418</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>2</v>
       </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
         <v>0.1948786507610037</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
         <v>0.1202185792349727</v>
       </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
         <v>0.1656804733727811</v>
       </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
         <v>0.1508224617129892</v>
       </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
         <v>0.08974358974358974</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AE10" t="n">
         <v>0.05</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AF10" t="n">
         <v>0.1016483516483516</v>
       </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
         <v>0.07339901477832513</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AI10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1539,104 +1639,114 @@
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>108.574</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>94.038</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>82.39999999999999</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>4</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>13.6</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>44.04</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve"> Martin had treated her badly sometimes, and well, Martin did take Sophia for granted, although Sophia was better than anything Martin could ever hope for, and Martin could go on and on and on about all the things that ended poorly, but it was beside the point.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.03058387395736794</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>0.06834586369818754</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.04688702486964957</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.08418699582492685</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>0.0539444691064988</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>0.07059922016957464</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>0.07122893599885187</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>0.02962344427213806</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>0.03647079893843925</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>0.04862897958024481</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>0.1225939877660442</v>
       </c>
-      <c r="T11" t="n">
+      <c r="V11" t="n">
         <v>0.08516225203531706</v>
       </c>
-      <c r="U11" t="n">
+      <c r="W11" t="n">
         <v>0.06870882740447957</v>
       </c>
-      <c r="V11" t="n">
+      <c r="X11" t="n">
         <v>0.07432930718328949</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Y11" t="n">
         <v>0.1227588904781115</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Z11" t="n">
         <v>0.06119105578323525</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AA11" t="n">
         <v>0.06826426594272329</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AB11" t="n">
         <v>0.05208333333333334</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AC11" t="n">
         <v>0.112456289153758</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AD11" t="n">
         <v>0.09726430976430978</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AE11" t="n">
         <v>0.07009503848115865</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AF11" t="n">
         <v>0.03759259259259259</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AG11" t="n">
         <v>0.04300445930880714</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AH11" t="n">
         <v>0.03125</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AI11" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -1644,104 +1754,114 @@
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>116.815</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>109.381</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>100</v>
       </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve"> Martin learned the lesson, or so he told everybody, not understanding what the lesson was and how the heck was he supposed to learn it.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.1022875816993464</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>0.0616800920598389</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.07703997248297026</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>0.0698237664248739</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>0.02316593161663584</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>0.03868796898250568</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>0.04901666781996356</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>0.02543005517689062</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>0.01701002446917673</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.08904964950046919</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>1.5</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.1434027777777778</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>0.1584991447052551</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>0.08377836226154689</v>
       </c>
-      <c r="V12" t="n">
+      <c r="X12" t="n">
         <v>0.02941176470588236</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Y12" t="n">
         <v>0.1052345807146015</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Z12" t="n">
         <v>0.1462304955938233</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AA12" t="n">
         <v>0.05944207583551846</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AB12" t="n">
         <v>0.03933963288801998</v>
       </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
         <v>0.02380952380952381</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AE12" t="n">
         <v>0.1230044828608147</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AF12" t="n">
         <v>0.1194444444444445</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AG12" t="n">
         <v>0.03166035353535353</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AH12" t="n">
         <v>0.03950617283950617</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AI12" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -1749,104 +1869,114 @@
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>122.426</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>118.498</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>79.40000000000001</v>
       </c>
-      <c r="C13" t="n">
+      <c r="E13" t="n">
         <v>20.6</v>
       </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
         <v>-38.18</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve"> Martin's mom identified his usual habit and spoke to him, annoyed.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>0.02095036500312085</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.01984126984126984</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>0.01096491228070175</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>0.006289308176100628</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>0.05388961321164711</v>
       </c>
-      <c r="P13" t="n">
+      <c r="R13" t="n">
         <v>0.04722375945397528</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>0.05772005772005772</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>0.75</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>0.04</v>
       </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
         <v>0.015625</v>
       </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
         <v>0.01063829787234043</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AB13" t="n">
         <v>0.01666666666666667</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AC13" t="n">
         <v>0.1547008547008547</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AD13" t="n">
         <v>0.07039128680919726</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AE13" t="n">
         <v>0.1414728682170543</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AF13" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AG13" t="n">
         <v>0.1222222222222222</v>
       </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1854,104 +1984,114 @@
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>132.385</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>123.228</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>83.5</v>
       </c>
-      <c r="C14" t="n">
+      <c r="E14" t="n">
         <v>16.5</v>
       </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>-67.56999999999999</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t xml:space="preserve">  I'm so fed up with you, Martin.  Listen to me.  This might sound a bit crazy, but have you explored the idea of seeing a healer about your painful breakup?</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.07740664601619567</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>0.03946796181410888</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.03550033335947917</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>0.04176190476190476</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>0.02961281719697736</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>0.03193768037518038</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>0.05156873061586176</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>0.01976495726495726</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>0.04307707007114275</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>0.06286094198854592</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>2</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>0.08789070296594946</v>
       </c>
-      <c r="T14" t="n">
+      <c r="V14" t="n">
         <v>0.2259692513368984</v>
       </c>
-      <c r="U14" t="n">
+      <c r="W14" t="n">
         <v>0.08541666666666667</v>
       </c>
-      <c r="V14" t="n">
+      <c r="X14" t="n">
         <v>0.111394783377542</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Y14" t="n">
         <v>0.06178396072013093</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Z14" t="n">
         <v>0.0503441461087638</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AA14" t="n">
         <v>0.05219780219780219</v>
       </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
       <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
         <v>0.09036796536796537</v>
       </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0.0108695652173913</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AG14" t="n">
         <v>0.02631578947368421</v>
       </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1959,104 +2099,114 @@
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>137.668</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>133.242</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>49.8</v>
       </c>
-      <c r="C15" t="n">
+      <c r="E15" t="n">
         <v>18.3</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>31.9</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G15" t="n">
         <v>35.32</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Wow, Mom, that was just a dumb idea.  I'm not that desperate.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.04813218390804597</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>0.01234567901234568</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.02914389799635701</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>0.0231729055258467</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>0.01041666666666667</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>0.06060606060606061</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>0.04626660558863949</v>
       </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
         <v>0.04580712788259959</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>0.07886904761904762</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>1.5</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>0.1538461538461539</v>
       </c>
-      <c r="T15" t="n">
+      <c r="V15" t="n">
         <v>0.1470588235294118</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
         <v>0.1494252873563219</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Y15" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
         <v>0.06593406593406594</v>
       </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
       <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
         <v>0.1948051948051948</v>
       </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
       <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
         <v>0.1052631578947368</v>
       </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -2064,104 +2214,114 @@
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>145.638</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>138.549</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>64.40000000000001</v>
       </c>
-      <c r="C16" t="n">
+      <c r="E16" t="n">
         <v>8.4</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>27.2</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
         <v>52.42</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Dearest, I wish you weren't.  Martin sometimes hated his mother for her harsh candor, but she had a point.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.04838709677419355</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>0.04347826086956521</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.06015094441198499</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>0.03205128205128205</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>0.1911839615921249</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>0.09256305860557101</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>0.0588235294117647</v>
       </c>
-      <c r="P16" t="n">
+      <c r="R16" t="n">
         <v>0.05125439965372305</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.0674161132038065</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>0.1215538847117795</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
         <v>0.1372549019607843</v>
       </c>
-      <c r="U16" t="n">
+      <c r="W16" t="n">
         <v>0.1035087719298246</v>
       </c>
-      <c r="V16" t="n">
+      <c r="X16" t="n">
         <v>0.04545454545454545</v>
       </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
         <v>0.05263157894736842</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AA16" t="n">
         <v>0.02419354838709678</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AB16" t="n">
         <v>0.06060606060606061</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AC16" t="n">
         <v>0.09222199298535176</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AD16" t="n">
         <v>0.01851851851851852</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AE16" t="n">
         <v>0.09412298615838439</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AF16" t="n">
         <v>0.07364779874213837</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AG16" t="n">
         <v>0.2122688655672164</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AH16" t="n">
         <v>0.0611672278338945</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AI16" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -2169,73 +2329,77 @@
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>152.486</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>146.759</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>89.90000000000001</v>
       </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
         <v>10.1</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
         <v>20.23</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t xml:space="preserve"> Fine, Mom, I'll check it out, Martin said dispassionately while he hung up and mumbled to himself.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>0.04498792270531401</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>0.01660309625308503</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>0.01474073181507812</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>0.03537079262761147</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>0.06483395342428</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>0.04964448368807509</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>0.07674346554490817</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>0.6</v>
       </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
         <v>0.05263157894736842</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
@@ -2243,30 +2407,36 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
         <v>0.02702702702702703</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AB17" t="n">
         <v>0.1211366290385364</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AC17" t="n">
         <v>0.03963221306277743</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AD17" t="n">
         <v>0.1148162840283632</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AE17" t="n">
         <v>0.05359652057544329</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AF17" t="n">
         <v>0.08791505918818215</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AG17" t="n">
         <v>0.09189365064609092</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AH17" t="n">
         <v>0.01955888472742405</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AI17" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -2274,104 +2444,114 @@
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>163.439</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>153.327</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>73.2</v>
       </c>
-      <c r="C18" t="n">
+      <c r="E18" t="n">
         <v>14</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>12.8</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>15.31</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t xml:space="preserve">  What do I have to lose?  Martin woke up at dawn the next morning and anxiously scanned the internet for the combination of best and inexpensive Healer.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>0.03100775193798449</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>0.0425531914893617</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>0.02185792349726776</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>0.09445100354191265</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>0.09045893719806763</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>0.09173933032548642</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>0.0746996996996997</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.07460738495221254</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
         <v>0.08749999999999999</v>
       </c>
-      <c r="V18" t="n">
+      <c r="X18" t="n">
         <v>0.09615384615384616</v>
       </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
         <v>0.01724137931034483</v>
       </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
         <v>0.1627906976744186</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AC18" t="n">
         <v>0.2246503496503497</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AD18" t="n">
         <v>0.08571428571428572</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AE18" t="n">
         <v>0.02380952380952381</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AF18" t="n">
         <v>0.2525987525987526</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AG18" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AH18" t="n">
         <v>0.2142857142857143</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AI18" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -2379,104 +2559,114 @@
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>170.414</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>164.22</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>77.2</v>
       </c>
-      <c r="C19" t="n">
+      <c r="E19" t="n">
         <v>5.7</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>17.1</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
         <v>58.59</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t xml:space="preserve"> Before long, Martin understood that knowing nothing about the subject, it was hard to figure out which Healer was the best.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>0.02811584403876493</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>0.05964213754137709</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.0483124908585637</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.02439024390243902</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>0.01709401709401709</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>0.06154616017184733</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>0.04640023315282791</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>0.05500509911868526</v>
       </c>
-      <c r="P19" t="n">
+      <c r="R19" t="n">
         <v>0.07987952217279405</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
         <v>0.06390556255718637</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="S19" t="n">
+      <c r="U19" t="n">
         <v>0.1047248803827751</v>
       </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
         <v>0.08732558139534885</v>
       </c>
-      <c r="V19" t="n">
+      <c r="X19" t="n">
         <v>0.1087914023960536</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Y19" t="n">
         <v>0.1090025457070123</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Z19" t="n">
         <v>0.05965532479010163</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AA19" t="n">
         <v>0.02649006622516556</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AB19" t="n">
         <v>0.09166022419791264</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AC19" t="n">
         <v>0.1615316316118627</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AD19" t="n">
         <v>0.09785289424053387</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AE19" t="n">
         <v>0.06419457735247208</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AF19" t="n">
         <v>0.1035137701804368</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AG19" t="n">
         <v>0.03246753246753246</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AH19" t="n">
         <v>0.0297661233167966</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AI19" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2484,67 +2674,71 @@
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>174.724</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>171.256</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>100</v>
       </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve"> He would have to compromise for the most inexpensive one he could get.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>0.08695652173913042</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>0.25</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>0.09090909090909093</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
         <v>0.1162790697674418</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
         <v>1</v>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
@@ -2582,6 +2776,12 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2589,34 +2789,38 @@
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>179.791</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>174.704</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
         <v>24.4</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
         <v>44.04</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t xml:space="preserve"> Andre the Giant, hypnosis and physio specialist, customer satisfaction guaranteed.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
@@ -2627,29 +2831,29 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>0.06451612903225806</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>0.1851851851851852</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>0.08</v>
       </c>
-      <c r="P21" t="n">
+      <c r="R21" t="n">
         <v>0.125</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="S21" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
@@ -2687,6 +2891,12 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2694,104 +2904,114 @@
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>188.623</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>180.092</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>70.89999999999999</v>
       </c>
-      <c r="C22" t="n">
+      <c r="E22" t="n">
         <v>4.6</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>24.5</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
         <v>82.91</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t xml:space="preserve"> The combination was kind of strange, but just thinking about The Princess Bride, which was Martin's all-time favorite film by far, made the choice much more easy.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.02148846960167715</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>0.0671963412607624</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.05818483360121537</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.06038997495106454</v>
       </c>
-      <c r="L22" t="n">
+      <c r="N22" t="n">
         <v>0.03774165183225794</v>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>0.03691830887976722</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>0.02633141153032589</v>
       </c>
-      <c r="O22" t="n">
+      <c r="Q22" t="n">
         <v>0.03084066996183432</v>
       </c>
-      <c r="P22" t="n">
+      <c r="R22" t="n">
         <v>0.03551791629027401</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>0.03047180716535555</v>
       </c>
-      <c r="R22" t="n">
+      <c r="T22" t="n">
         <v>2.25</v>
       </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
         <v>0.02881183069862315</v>
       </c>
-      <c r="T22" t="n">
+      <c r="V22" t="n">
         <v>0.1200110422335328</v>
       </c>
-      <c r="U22" t="n">
+      <c r="W22" t="n">
         <v>0.06318939560843063</v>
       </c>
-      <c r="V22" t="n">
+      <c r="X22" t="n">
         <v>0.0891338204778233</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Y22" t="n">
         <v>0.09229424013477171</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Z22" t="n">
         <v>0.1323803860853844</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AA22" t="n">
         <v>0.01904761904761905</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AB22" t="n">
         <v>0.09872979633253605</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AC22" t="n">
         <v>0.03636363636363636</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AD22" t="n">
         <v>0.08128458918688804</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AE22" t="n">
         <v>0.05452744765138653</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AF22" t="n">
         <v>0.06161230074273553</v>
       </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
         <v>0.05395965504152059</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AI22" t="n">
         <v>0.8571428571428571</v>
       </c>
     </row>
@@ -2799,104 +3019,114 @@
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>191.748</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>188.664</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>100</v>
       </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t xml:space="preserve"> A deep voice answered Martin's call.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>0.05714285714285713</v>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>0.1167341430499325</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>0.04750558451228593</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>0.05789473684210526</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>0.08842265614180861</v>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
         <v>0.1114653663415854</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
         <v>1</v>
       </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
       <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
         <v>0.1212121212121212</v>
       </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Z23" t="n">
         <v>0.1016731016731017</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AA23" t="n">
         <v>0.0125</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AB23" t="n">
         <v>0.2806060606060606</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AC23" t="n">
         <v>0.1744421906693712</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AD23" t="n">
         <v>0.1071428571428571</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AE23" t="n">
         <v>0.119047619047619</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AF23" t="n">
         <v>0.046875</v>
       </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
         <v>0.09259259259259259</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AI23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2904,104 +3134,114 @@
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>196.595</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>192.269</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>51.1</v>
       </c>
-      <c r="C24" t="n">
+      <c r="E24" t="n">
         <v>17.6</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>31.2</v>
       </c>
-      <c r="E24" t="n">
+      <c r="G24" t="n">
         <v>34</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Today's your lucky day, Mr. Williams.  Somehow a fake name felt comforting.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>0.02696078431372549</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.001221001221001221</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>0.07869059632848098</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>0.1048014558350054</v>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>0.07637195121951219</v>
       </c>
-      <c r="P24" t="n">
+      <c r="R24" t="n">
         <v>0.0544429851239712</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>0.09779433938047695</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>0.6</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0.171875</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>0.1139240506329114</v>
       </c>
-      <c r="U24" t="n">
+      <c r="W24" t="n">
         <v>0.04365184988022358</v>
       </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
         <v>0.01245551601423488</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Z24" t="n">
         <v>0.04615384615384616</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AA24" t="n">
         <v>0.01536633966891478</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AB24" t="n">
         <v>0.009652509652509652</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AC24" t="n">
         <v>0.015625</v>
       </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
         <v>0.1064923036210471</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AF24" t="n">
         <v>0.1415094339622641</v>
       </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0</v>
-      </c>
       <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -3009,104 +3249,114 @@
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>203.344</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>197.296</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>85.59999999999999</v>
       </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
         <v>14.4</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
         <v>52.16</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t xml:space="preserve"> I have a place at 1.30 p.m. today, but it's going to be cold, so be sure to bring a coat.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>0.02521739130434782</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>0.04420216703681271</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.0477952903649498</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.03416879795396419</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>0.03125268817204301</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>0.08967975356128602</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>0.04549406532165153</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>0.04494432071269489</v>
       </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
         <v>0.04201505476231843</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>0.04847513651127308</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>0.09099225139905295</v>
       </c>
-      <c r="T25" t="n">
+      <c r="V25" t="n">
         <v>0.06901647286821705</v>
       </c>
-      <c r="U25" t="n">
+      <c r="W25" t="n">
         <v>0.1085714285714286</v>
       </c>
-      <c r="V25" t="n">
+      <c r="X25" t="n">
         <v>0.06451612903225806</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Y25" t="n">
         <v>0.1901795363581596</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Z25" t="n">
         <v>0.1226604167902797</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AA25" t="n">
         <v>0.03600464576074332</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AB25" t="n">
         <v>0.08451342471961029</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AC25" t="n">
         <v>0.1069096481876333</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AD25" t="n">
         <v>0.08579770967532045</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AE25" t="n">
         <v>0.1036579075130477</v>
       </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
       <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
         <v>0.05666746612303633</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AI25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3114,67 +3364,71 @@
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>213.722</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>204.809</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>77.90000000000001</v>
       </c>
-      <c r="C26" t="n">
+      <c r="E26" t="n">
         <v>13.1</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>9</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>-25</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t xml:space="preserve"> Martin arrived at Andre's clinic at 1.27, and Andre, that to Martin's dissatisfaction was a surprisingly small man, invited him in.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>0.02564102564102564</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.04163059163059164</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.03703235591506572</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>0.03475274725274725</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>0.1046679166366193</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>0.05638769984965353</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>0.05796145164090989</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>0.03791469194312796</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>0.05431939528466015</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
@@ -3182,36 +3436,42 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
         <v>0.0772520716385993</v>
       </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
       <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
         <v>0.1534127289025483</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AC26" t="n">
         <v>0.1943609765043627</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AD26" t="n">
         <v>0.1209620253164557</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AE26" t="n">
         <v>0.1373400579060428</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AF26" t="n">
         <v>0.05376344086021505</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AG26" t="n">
         <v>0.06517094017094016</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AH26" t="n">
         <v>0.110019825177976</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AI26" t="n">
         <v>0.375</v>
       </c>
     </row>
@@ -3219,67 +3479,71 @@
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>216.807</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>213.742</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>60.6</v>
       </c>
-      <c r="C27" t="n">
+      <c r="E27" t="n">
         <v>39.4</v>
       </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
         <v>-38.18</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t xml:space="preserve"> I dislike Thursdays, Andre said.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>0.0498092887592551</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
         <v>0.04422219544523436</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>0.04728884847106968</v>
       </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
         <v>0.04548517520215634</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>0.04259713437459662</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
@@ -3296,27 +3560,33 @@
         <v>0</v>
       </c>
       <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
         <v>0.07084468664850137</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AC27" t="n">
         <v>0.07926442612555486</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AD27" t="n">
         <v>0.08677542519958348</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AE27" t="n">
         <v>0.07862161257945802</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AF27" t="n">
         <v>0.06673920928545521</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AG27" t="n">
         <v>0.05475504322766571</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AH27" t="n">
         <v>0.03911776945484811</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -3324,104 +3594,114 @@
       <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>221.974</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>216.867</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>81.10000000000001</v>
       </c>
-      <c r="C28" t="n">
+      <c r="E28" t="n">
         <v>18.9</v>
       </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
         <v>-42.15</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t xml:space="preserve">  For some reason, everyone seems to be ill.  I know what you mean.</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>0.01606875934230194</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.05303238421010854</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>0.02860395789637225</v>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
         <v>0.01492537313432836</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>0.06359282963125737</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>0.07816006600660064</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>0.0136986301369863</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>0.02337391181258405</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
         <v>0.06306740082472909</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>4</v>
       </c>
-      <c r="S28" t="n">
+      <c r="U28" t="n">
         <v>0.04819471308833011</v>
       </c>
-      <c r="T28" t="n">
+      <c r="V28" t="n">
         <v>0.04684873949579832</v>
       </c>
-      <c r="U28" t="n">
+      <c r="W28" t="n">
         <v>0.06932136937396405</v>
       </c>
-      <c r="V28" t="n">
+      <c r="X28" t="n">
         <v>0.03194263363754889</v>
       </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
         <v>0.1053288918873334</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AA28" t="n">
         <v>0.02272727272727273</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AB28" t="n">
         <v>0.09597402597402599</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AC28" t="n">
         <v>0.05697791164658635</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AD28" t="n">
         <v>0.07352941176470588</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AE28" t="n">
         <v>0.03846675712347354</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AF28" t="n">
         <v>0.1330498255336617</v>
       </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
         <v>0.09036292382565675</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AI28" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3429,104 +3709,114 @@
       <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>228.083</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>221.994</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
         <v>8.6</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>12.8</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t xml:space="preserve"> I used to be in the bathroom tissue industry, Martin replied, feeling that was an unconventional response.</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>0.01037613488975357</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.01298701298701299</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>0.03196111326192626</v>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
         <v>0.03336940836940837</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>0.1748818060576808</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>0.05558808222742648</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>0.06049783549783549</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>0.01510757332675141</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>0.1326694139194139</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>3</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
         <v>0.06818181818181819</v>
       </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
         <v>0.0429042904290429</v>
       </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
         <v>0.108065953654189</v>
       </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
       <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
         <v>0.1646903820816864</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AC29" t="n">
         <v>0.165510153010153</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AD29" t="n">
         <v>0.08957002979991487</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AE29" t="n">
         <v>0.1050559926964421</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AF29" t="n">
         <v>0.07317073170731707</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AG29" t="n">
         <v>0.099822695035461</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AH29" t="n">
         <v>0.09026754026754026</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AI29" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -3534,104 +3824,114 @@
       <c r="A30" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>233.181</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>228.232</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>83.8</v>
       </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
         <v>16.2</v>
       </c>
-      <c r="E30" t="n">
+      <c r="G30" t="n">
         <v>40.19</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t xml:space="preserve"> So, are you interested in physio work, or you came here only for hypnosis session?</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>0.0967376197667216</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>0.06449634725110648</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>0.09091336832769574</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.05507278669043375</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>0.05950078003120125</v>
       </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>0.01824817518248175</v>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
         <v>0.0168997668997669</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>0.02102102102102102</v>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>2</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.03548387096774194</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>0.1136363636363636</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>0.1049382716049383</v>
       </c>
-      <c r="V30" t="n">
+      <c r="X30" t="n">
         <v>0.1138888888888889</v>
       </c>
-      <c r="W30" t="n">
+      <c r="Y30" t="n">
         <v>0.1462918660287081</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Z30" t="n">
         <v>0.1086153846153846</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AA30" t="n">
         <v>0.05423728813559322</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AB30" t="n">
         <v>0.1470588235294118</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AC30" t="n">
         <v>0.04261363636363636</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AD30" t="n">
         <v>0.03214285714285714</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AE30" t="n">
         <v>0.06097560975609756</v>
       </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
       <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
         <v>0.0673076923076923</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AI30" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3639,104 +3939,114 @@
       <c r="A31" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>239.073</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>233.743</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>62.2</v>
       </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
         <v>37.8</v>
       </c>
-      <c r="E31" t="n">
+      <c r="G31" t="n">
         <v>81.76000000000001</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Andre asked.  Just the hypnosis, please.  My neck seems to be just perfect these days, thank you.</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>0.01515151515151515</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>0.05419212133979355</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>0.06097560975609756</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>0.09102564102564104</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
         <v>0.02830188679245283</v>
       </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
         <v>0.03291139240506329</v>
       </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
         <v>0.01656626506024097</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>0.4</v>
       </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
       <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
         <v>0.06976744186046512</v>
       </c>
-      <c r="V31" t="n">
+      <c r="X31" t="n">
         <v>0.0379746835443038</v>
       </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
         <v>0.08265186915887851</v>
       </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
         <v>0.3126901347240331</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AC31" t="n">
         <v>0.1049875998897768</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AD31" t="n">
         <v>0.14</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AE31" t="n">
         <v>0.1136363636363636</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AF31" t="n">
         <v>0.1027472527472527</v>
       </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
         <v>0.05708502024291498</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AI31" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -3744,67 +4054,71 @@
       <c r="A32" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>244.042</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>239.514</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>58.3</v>
       </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
         <v>41.7</v>
       </c>
-      <c r="E32" t="n">
+      <c r="G32" t="n">
         <v>61.24000000000001</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Martin replied confidently.  Okay, dude.  Andre replied and coughed.</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>0.03571428571428571</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>0.206896551724138</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
         <v>0.06060606060606061</v>
       </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
       <c r="U32" t="n">
         <v>0</v>
       </c>
@@ -3842,6 +4156,12 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3849,67 +4169,71 @@
       <c r="A33" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>251.815</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>245.745</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>68</v>
       </c>
-      <c r="C33" t="n">
+      <c r="E33" t="n">
         <v>11.7</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>20.4</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>42.15</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t xml:space="preserve">  What seems to be worrying you, Mr. Williams?  It's Sophia, the best girl on planet Earth.</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>0.08108108108108107</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>0.03488372093023256</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>0.03488372093023256</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.078125</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>0.1729583975346687</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>0.05113636363636364</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>0.01428571428571428</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>0.03968253968253968</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>0.02816901408450704</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
       <c r="U33" t="n">
         <v>0</v>
       </c>
@@ -3947,6 +4271,12 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3954,104 +4284,114 @@
       <c r="A34" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>258.402</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>252.556</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>78.2</v>
       </c>
-      <c r="C34" t="n">
+      <c r="E34" t="n">
         <v>15.8</v>
       </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
         <v>5.899999999999999</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>-52.77</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t xml:space="preserve">  I can't stop thinking of her.  The wedding was supposed to happen in the summer, but I was scared to marry.</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>0.02848699763593381</v>
       </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>0.008547008547008546</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>0.01626016260162602</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
         <v>0.1027628288767876</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>0.08948440637066936</v>
       </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
         <v>0.05418218561110658</v>
       </c>
-      <c r="P34" t="n">
+      <c r="R34" t="n">
         <v>0.09565155402534042</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
         <v>0.1179914221580888</v>
       </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>3</v>
       </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
         <v>0.08481532147742818</v>
       </c>
-      <c r="U34" t="n">
+      <c r="W34" t="n">
         <v>0.1012059973924381</v>
       </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
         <v>0.05</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Z34" t="n">
         <v>0.05300366504809213</v>
       </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
         <v>0.1645502694323466</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AC34" t="n">
         <v>0.0816614420062696</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AD34" t="n">
         <v>0.08297413793103448</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AE34" t="n">
         <v>0.1560724821893733</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AF34" t="n">
         <v>0.117287784679089</v>
       </c>
-      <c r="AE34" t="n">
+      <c r="AG34" t="n">
         <v>0.02906976744186046</v>
       </c>
-      <c r="AF34" t="n">
+      <c r="AH34" t="n">
         <v>0.1195671603677222</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AI34" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4059,104 +4399,114 @@
       <c r="A35" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>266.431</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>259.523</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="C35" t="n">
+      <c r="E35" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="D35" t="n">
+      <c r="F35" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>0.18</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t xml:space="preserve">  I'm totally obsessed with Sophia.  I dream about Sophia constantly, and I see her image in practically every woman I meet.</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>0.02351846930640446</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>0.08610220111837918</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.07216428078369087</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.03045843045843045</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>0.04664570230607967</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>0.04269019857543482</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>0.0378435927216415</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>0.02974493480822595</v>
       </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
         <v>0.09838544785444835</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="S35" t="n">
         <v>0.07842289460701952</v>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>1.5</v>
       </c>
-      <c r="S35" t="n">
+      <c r="U35" t="n">
         <v>0.06111111111111111</v>
       </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
       <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
         <v>0.06878306878306878</v>
       </c>
-      <c r="W35" t="n">
+      <c r="Y35" t="n">
         <v>0.05128205128205129</v>
       </c>
-      <c r="X35" t="n">
+      <c r="Z35" t="n">
         <v>0.1837962962962963</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AA35" t="n">
         <v>0.02164502164502164</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AB35" t="n">
         <v>0.08641975308641975</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AC35" t="n">
         <v>0.1257802180220363</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AD35" t="n">
         <v>0.1097373737373737</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AE35" t="n">
         <v>0.09214340198321891</v>
       </c>
-      <c r="AD35" t="n">
+      <c r="AF35" t="n">
         <v>0.1179332715477294</v>
       </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
         <v>0.1407241508025383</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AI35" t="n">
         <v>0.4285714285714285</v>
       </c>
     </row>
@@ -4164,67 +4514,71 @@
       <c r="A36" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>271.116</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>267.932</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>75.2</v>
       </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
         <v>24.8</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>51.06</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t xml:space="preserve"> To be honest, you are the 30th counselor I've spoken to.</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0.0703125</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>0.09183673469387756</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>0.1135778635778636</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>0.04878048780487805</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>0.0711590296495957</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>0.01</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>0.05208333333333334</v>
       </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
       <c r="U36" t="n">
         <v>0</v>
       </c>
@@ -4262,6 +4616,12 @@
         <v>0</v>
       </c>
       <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4269,104 +4629,114 @@
       <c r="A37" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>283.083</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>275.853</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
         <v>5.899999999999999</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>13.26</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t xml:space="preserve"> Martin didn't understand the relevance of the question, though he replied nevertheless, I'm not crazy about it, but I eat a little now and then.</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>0.05554626066588589</v>
       </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
         <v>0.05740193325162127</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.0421759137848506</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>0.03680158225612771</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>0.06385399523651403</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>0.09679483649993652</v>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
         <v>0.02491582491582492</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
         <v>0.02023988005997001</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
         <v>0.07974234124568878</v>
       </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>3</v>
       </c>
-      <c r="S37" t="n">
+      <c r="U37" t="n">
         <v>0.0274914089347079</v>
       </c>
-      <c r="T37" t="n">
+      <c r="V37" t="n">
         <v>0.07301587301587302</v>
       </c>
-      <c r="U37" t="n">
+      <c r="W37" t="n">
         <v>0.02830188679245283</v>
       </c>
-      <c r="V37" t="n">
+      <c r="X37" t="n">
         <v>0.04883710548636222</v>
       </c>
-      <c r="W37" t="n">
+      <c r="Y37" t="n">
         <v>0.1025354213273676</v>
       </c>
-      <c r="X37" t="n">
+      <c r="Z37" t="n">
         <v>0.04970760233918128</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="AA37" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AB37" t="n">
         <v>0.08511801402019421</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AC37" t="n">
         <v>0.02150537634408602</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AD37" t="n">
         <v>0.08055555555555556</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AE37" t="n">
         <v>0.04301075268817204</v>
       </c>
-      <c r="AD37" t="n">
+      <c r="AF37" t="n">
         <v>0.03300330033003301</v>
       </c>
-      <c r="AE37" t="n">
+      <c r="AG37" t="n">
         <v>0.0430172068827531</v>
       </c>
-      <c r="AF37" t="n">
+      <c r="AH37" t="n">
         <v>0.05720245937637242</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AI37" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -4374,104 +4744,114 @@
       <c r="A38" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>292.135</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>283.143</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>89.3</v>
       </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
         <v>10.7</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>45.88</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t xml:space="preserve"> Just keep your eyes on the Kit Kat, Andre replied, while he started to gently swing a small Kit Kat that was dangling from a cord.</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
         <v>0.03509136212624585</v>
       </c>
-      <c r="L38" t="n">
+      <c r="N38" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>0.1198298460480229</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>0.0684896433945065</v>
       </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
         <v>0.07725977725977726</v>
       </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
         <v>0.04557673509286413</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="S38" t="n">
         <v>0.04405818979763694</v>
       </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>0.4444444444444444</v>
       </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
         <v>0.1066666666666667</v>
       </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
       <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
         <v>0.05426356589147287</v>
       </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
         <v>0.02298850574712644</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AB38" t="n">
         <v>0.1502675819374584</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AC38" t="n">
         <v>0.03184713375796178</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AD38" t="n">
         <v>0.08358847736625515</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AE38" t="n">
         <v>0.05805656307043122</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AF38" t="n">
         <v>0.1144049187527448</v>
       </c>
-      <c r="AE38" t="n">
+      <c r="AG38" t="n">
         <v>0.06353178784685633</v>
       </c>
-      <c r="AF38" t="n">
+      <c r="AH38" t="n">
         <v>0.09677595628415302</v>
       </c>
-      <c r="AG38" t="n">
+      <c r="AI38" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -4479,104 +4859,114 @@
       <c r="A39" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>297.302</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>293.657</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>84.5</v>
       </c>
-      <c r="C39" t="n">
+      <c r="E39" t="n">
         <v>15.5</v>
       </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
         <v>-29.6</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t xml:space="preserve">  Aren't you supposed to do that with a pocket clock?  Martin asked doubtfully.</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>0.2777777777777777</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>0.1259625962596259</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>0.1504273504273504</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>0.02222222222222223</v>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
         <v>0.01886792452830189</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>0.0379746835443038</v>
       </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
         <v>0.0219409282700422</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>0.04255663430420712</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
         <v>0.1132086788713295</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>1</v>
       </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
         <v>0.08139534883720931</v>
       </c>
-      <c r="U39" t="n">
+      <c r="W39" t="n">
         <v>0.2043828264758497</v>
       </c>
-      <c r="V39" t="n">
+      <c r="X39" t="n">
         <v>0.0379746835443038</v>
       </c>
-      <c r="W39" t="n">
+      <c r="Y39" t="n">
         <v>0.1</v>
       </c>
-      <c r="X39" t="n">
+      <c r="Z39" t="n">
         <v>0.1040334481062469</v>
       </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
         <v>0.1625660652451248</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AC39" t="n">
         <v>0.05235602094240838</v>
       </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
         <v>0.05128205128205128</v>
       </c>
-      <c r="AD39" t="n">
+      <c r="AF39" t="n">
         <v>0.06428571428571428</v>
       </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
         <v>0.1307692307692308</v>
       </c>
-      <c r="AG39" t="n">
+      <c r="AI39" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4584,49 +4974,53 @@
       <c r="A40" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>303.21</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>297.342</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>66.2</v>
       </c>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="n">
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
         <v>33.8</v>
       </c>
-      <c r="E40" t="n">
+      <c r="G40" t="n">
         <v>55.74</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t xml:space="preserve"> Put your faith in Andre, and everything will be just fine.</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>0.1293103448275862</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>0.1415929203539823</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>0.125</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>0.2520325203252032</v>
       </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
@@ -4637,35 +5031,35 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
         <v>0.5</v>
       </c>
-      <c r="S40" t="n">
+      <c r="U40" t="n">
         <v>0.2619047619047619</v>
       </c>
-      <c r="T40" t="n">
+      <c r="V40" t="n">
         <v>0.4</v>
       </c>
-      <c r="U40" t="n">
+      <c r="W40" t="n">
         <v>0.7058823529411765</v>
       </c>
-      <c r="V40" t="n">
+      <c r="X40" t="n">
         <v>0.06976744186046512</v>
       </c>
-      <c r="W40" t="n">
+      <c r="Y40" t="n">
         <v>0.2962962962962963</v>
       </c>
-      <c r="X40" t="n">
+      <c r="Z40" t="n">
         <v>0.1923076923076923</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AA40" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
       <c r="AB40" t="n">
         <v>0</v>
       </c>
@@ -4682,6 +5076,12 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4689,104 +5089,114 @@
       <c r="A41" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>313.372</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>303.494</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>66.3</v>
       </c>
-      <c r="C41" t="n">
+      <c r="E41" t="n">
         <v>8.1</v>
       </c>
-      <c r="D41" t="n">
+      <c r="F41" t="n">
         <v>25.7</v>
       </c>
-      <c r="E41" t="n">
+      <c r="G41" t="n">
         <v>65.71000000000001</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t xml:space="preserve">  Martin took a deep breath and tried not to laugh.  The next thing Martin remembered was slowly awakening and feeling like he could certainly use a good physio session.</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H41" t="n">
+      <c r="J41" t="n">
         <v>0.02416372728018449</v>
       </c>
-      <c r="I41" t="n">
+      <c r="K41" t="n">
         <v>0.02549071421147437</v>
       </c>
-      <c r="J41" t="n">
+      <c r="L41" t="n">
         <v>0.06170598689980109</v>
       </c>
-      <c r="K41" t="n">
+      <c r="M41" t="n">
         <v>0.04421968348130027</v>
       </c>
-      <c r="L41" t="n">
+      <c r="N41" t="n">
         <v>0.03428409138906592</v>
       </c>
-      <c r="M41" t="n">
+      <c r="O41" t="n">
         <v>0.07940583606383064</v>
       </c>
-      <c r="N41" t="n">
+      <c r="P41" t="n">
         <v>0.05644997073886064</v>
       </c>
-      <c r="O41" t="n">
+      <c r="Q41" t="n">
         <v>0.03548973189930636</v>
       </c>
-      <c r="P41" t="n">
+      <c r="R41" t="n">
         <v>0.03787414642521811</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="S41" t="n">
         <v>0.03633041779820836</v>
       </c>
-      <c r="R41" t="n">
+      <c r="T41" t="n">
         <v>1.25</v>
       </c>
-      <c r="S41" t="n">
+      <c r="U41" t="n">
         <v>0.07070148708236623</v>
       </c>
-      <c r="T41" t="n">
+      <c r="V41" t="n">
         <v>0.06674904609421134</v>
       </c>
-      <c r="U41" t="n">
+      <c r="W41" t="n">
         <v>0.0510149423892114</v>
       </c>
-      <c r="V41" t="n">
+      <c r="X41" t="n">
         <v>0.05097275112767761</v>
       </c>
-      <c r="W41" t="n">
+      <c r="Y41" t="n">
         <v>0.1037470065706497</v>
       </c>
-      <c r="X41" t="n">
+      <c r="Z41" t="n">
         <v>0.05759716191831052</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="AA41" t="n">
         <v>0.04291544180870915</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AB41" t="n">
         <v>0.09706864977949316</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AC41" t="n">
         <v>0.08608632023122302</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AD41" t="n">
         <v>0.1014993513344338</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AE41" t="n">
         <v>0.08571414027042376</v>
       </c>
-      <c r="AD41" t="n">
+      <c r="AF41" t="n">
         <v>0.02840608465608465</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AG41" t="n">
         <v>0.05674859742747673</v>
       </c>
-      <c r="AF41" t="n">
+      <c r="AH41" t="n">
         <v>0.06306231651409316</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AI41" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4794,104 +5204,114 @@
       <c r="A42" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>318.638</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>313.992</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>81.5</v>
       </c>
-      <c r="C42" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" t="n">
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
         <v>18.5</v>
       </c>
-      <c r="E42" t="n">
+      <c r="G42" t="n">
         <v>52.66999999999999</v>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t xml:space="preserve"> When Martin exited Andre's clinic an hour later, he felt happier than he felt for years.</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>0.06608220211161388</v>
       </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
         <v>0.09116389213619991</v>
       </c>
-      <c r="N42" t="n">
+      <c r="P42" t="n">
         <v>0.009297520661157025</v>
       </c>
-      <c r="O42" t="n">
+      <c r="Q42" t="n">
         <v>0.08522202258726899</v>
       </c>
-      <c r="P42" t="n">
+      <c r="R42" t="n">
         <v>0.05298419476132815</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="S42" t="n">
         <v>0.07513101576364965</v>
       </c>
-      <c r="R42" t="n">
+      <c r="T42" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="S42" t="n">
+      <c r="U42" t="n">
         <v>0.1938875786163522</v>
       </c>
-      <c r="T42" t="n">
+      <c r="V42" t="n">
         <v>0.1139240506329114</v>
       </c>
-      <c r="U42" t="n">
+      <c r="W42" t="n">
         <v>0.05550699300699301</v>
       </c>
-      <c r="V42" t="n">
+      <c r="X42" t="n">
         <v>0.0130718954248366</v>
       </c>
-      <c r="W42" t="n">
+      <c r="Y42" t="n">
         <v>0.01851851851851852</v>
       </c>
-      <c r="X42" t="n">
+      <c r="Z42" t="n">
         <v>0.04615384615384616</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="AA42" t="n">
         <v>0.008928571428571428</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AB42" t="n">
         <v>0.05172413793103448</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AC42" t="n">
         <v>0.02147239263803681</v>
       </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="n">
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
         <v>0.1012658227848101</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AF42" t="n">
         <v>0.1599658098011903</v>
       </c>
-      <c r="AE42" t="n">
+      <c r="AG42" t="n">
         <v>0.01458333333333333</v>
       </c>
-      <c r="AF42" t="n">
+      <c r="AH42" t="n">
         <v>0.01181102362204724</v>
       </c>
-      <c r="AG42" t="n">
+      <c r="AI42" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -4899,104 +5319,114 @@
       <c r="A43" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>325.407</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>319.7</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
         <v>51.2</v>
       </c>
-      <c r="C43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" t="n">
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
         <v>48.8</v>
       </c>
-      <c r="E43" t="n">
+      <c r="G43" t="n">
         <v>90.81</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t xml:space="preserve">  It was like a blessing.  Martin's neck was relaxed, plus he felt rising optimism in his soul.</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H43" t="n">
+      <c r="J43" t="n">
         <v>0.003258145363408521</v>
       </c>
-      <c r="I43" t="n">
+      <c r="K43" t="n">
         <v>0.02960057313062014</v>
       </c>
-      <c r="J43" t="n">
+      <c r="L43" t="n">
         <v>0.004944931445268599</v>
       </c>
-      <c r="K43" t="n">
+      <c r="M43" t="n">
         <v>0.03046795177440229</v>
       </c>
-      <c r="L43" t="n">
+      <c r="N43" t="n">
         <v>0.004048582995951417</v>
       </c>
-      <c r="M43" t="n">
+      <c r="O43" t="n">
         <v>0.08382846809609919</v>
       </c>
-      <c r="N43" t="n">
+      <c r="P43" t="n">
         <v>0.02621722846441947</v>
       </c>
-      <c r="O43" t="n">
+      <c r="Q43" t="n">
         <v>0.06577380952380953</v>
       </c>
-      <c r="P43" t="n">
+      <c r="R43" t="n">
         <v>0.0261437908496732</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="S43" t="n">
         <v>0.06967741935483872</v>
       </c>
-      <c r="R43" t="n">
+      <c r="T43" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="S43" t="n">
+      <c r="U43" t="n">
         <v>0.09026275951557093</v>
       </c>
-      <c r="T43" t="n">
+      <c r="V43" t="n">
         <v>0.06236069641280121</v>
       </c>
-      <c r="U43" t="n">
+      <c r="W43" t="n">
         <v>0.02386039886039886</v>
       </c>
-      <c r="V43" t="n">
+      <c r="X43" t="n">
         <v>0.0347292342031142</v>
       </c>
-      <c r="W43" t="n">
+      <c r="Y43" t="n">
         <v>0.050287599390966</v>
       </c>
-      <c r="X43" t="n">
+      <c r="Z43" t="n">
         <v>0.04362318291944276</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="AA43" t="n">
         <v>0.007483609385783298</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="AB43" t="n">
         <v>0.1757294429708223</v>
       </c>
-      <c r="AA43" t="n">
+      <c r="AC43" t="n">
         <v>0.05572755417956656</v>
       </c>
-      <c r="AB43" t="n">
+      <c r="AD43" t="n">
         <v>0.09678571428571429</v>
       </c>
-      <c r="AC43" t="n">
+      <c r="AE43" t="n">
         <v>0.1074510932105869</v>
       </c>
-      <c r="AD43" t="n">
+      <c r="AF43" t="n">
         <v>0.08998548621190131</v>
       </c>
-      <c r="AE43" t="n">
+      <c r="AG43" t="n">
         <v>0.025</v>
       </c>
-      <c r="AF43" t="n">
+      <c r="AH43" t="n">
         <v>0.0131578947368421</v>
       </c>
-      <c r="AG43" t="n">
+      <c r="AI43" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -5004,104 +5434,114 @@
       <c r="A44" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>335.34</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>326.308</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
         <v>90.60000000000001</v>
       </c>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="n">
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
         <v>9.4</v>
       </c>
-      <c r="E44" t="n">
+      <c r="G44" t="n">
         <v>36.12</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t xml:space="preserve"> As he walked down the street, Martin noticed a woman that appeared exactly like Sophia, though after a second, he understood that he was fantasizing.</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H44" t="n">
+      <c r="J44" t="n">
         <v>0.01046664279746986</v>
       </c>
-      <c r="I44" t="n">
+      <c r="K44" t="n">
         <v>0.04645664282477479</v>
       </c>
-      <c r="J44" t="n">
+      <c r="L44" t="n">
         <v>0.0371622208879293</v>
       </c>
-      <c r="K44" t="n">
+      <c r="M44" t="n">
         <v>0.06594818747420383</v>
       </c>
-      <c r="L44" t="n">
+      <c r="N44" t="n">
         <v>0.02530957442991118</v>
       </c>
-      <c r="M44" t="n">
+      <c r="O44" t="n">
         <v>0.06434243660874232</v>
       </c>
-      <c r="N44" t="n">
+      <c r="P44" t="n">
         <v>0.01230117896098551</v>
       </c>
-      <c r="O44" t="n">
+      <c r="Q44" t="n">
         <v>0.05096381912449756</v>
       </c>
-      <c r="P44" t="n">
+      <c r="R44" t="n">
         <v>0.02610543028898963</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="S44" t="n">
         <v>0.02210242587601078</v>
       </c>
-      <c r="R44" t="n">
+      <c r="T44" t="n">
         <v>1.75</v>
       </c>
-      <c r="S44" t="n">
+      <c r="U44" t="n">
         <v>0.02669303015323776</v>
       </c>
-      <c r="T44" t="n">
+      <c r="V44" t="n">
         <v>0.06474556994752832</v>
       </c>
-      <c r="U44" t="n">
+      <c r="W44" t="n">
         <v>0.01737213403880071</v>
       </c>
-      <c r="V44" t="n">
+      <c r="X44" t="n">
         <v>0.001647446457990115</v>
       </c>
-      <c r="W44" t="n">
+      <c r="Y44" t="n">
         <v>0.06038794376840779</v>
       </c>
-      <c r="X44" t="n">
+      <c r="Z44" t="n">
         <v>0.0634990938632671</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="AA44" t="n">
         <v>0.03283539327017588</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AB44" t="n">
         <v>0.1033343398934797</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AC44" t="n">
         <v>0.039955900243309</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AD44" t="n">
         <v>0.07440968508615568</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AE44" t="n">
         <v>0.1153508771929825</v>
       </c>
-      <c r="AD44" t="n">
+      <c r="AF44" t="n">
         <v>0.07499227679950571</v>
       </c>
-      <c r="AE44" t="n">
+      <c r="AG44" t="n">
         <v>0.02964426877470356</v>
       </c>
-      <c r="AF44" t="n">
+      <c r="AH44" t="n">
         <v>0.03516391145979266</v>
       </c>
-      <c r="AG44" t="n">
+      <c r="AI44" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -5109,104 +5549,114 @@
       <c r="A45" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>341.209</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>335.641</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
         <v>63.6</v>
       </c>
-      <c r="C45" t="n">
+      <c r="E45" t="n">
         <v>11</v>
       </c>
-      <c r="D45" t="n">
+      <c r="F45" t="n">
         <v>25.4</v>
       </c>
-      <c r="E45" t="n">
+      <c r="G45" t="n">
         <v>36.12</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t xml:space="preserve"> Feeling good, he stopped to purchase a Kit Kat and continued walking home unburdened.</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H45" t="n">
+      <c r="J45" t="n">
         <v>0.01584266593826824</v>
       </c>
-      <c r="I45" t="n">
+      <c r="K45" t="n">
         <v>0.03969924812030075</v>
       </c>
-      <c r="J45" t="n">
+      <c r="L45" t="n">
         <v>0.01198979591836735</v>
       </c>
-      <c r="K45" t="n">
+      <c r="M45" t="n">
         <v>0.03301295075130995</v>
       </c>
-      <c r="L45" t="n">
+      <c r="N45" t="n">
         <v>0.06396782945455512</v>
       </c>
-      <c r="M45" t="n">
+      <c r="O45" t="n">
         <v>0.08033905698297573</v>
       </c>
-      <c r="N45" t="n">
+      <c r="P45" t="n">
         <v>0.068274145493429</v>
       </c>
-      <c r="O45" t="n">
+      <c r="Q45" t="n">
         <v>0.06424282818311607</v>
       </c>
-      <c r="P45" t="n">
+      <c r="R45" t="n">
         <v>0.05545421392470769</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="S45" t="n">
         <v>0.01980021893814998</v>
       </c>
-      <c r="R45" t="n">
+      <c r="T45" t="n">
         <v>2.333333333333333</v>
       </c>
-      <c r="S45" t="n">
+      <c r="U45" t="n">
         <v>0.0764673097534834</v>
       </c>
-      <c r="T45" t="n">
+      <c r="V45" t="n">
         <v>0.06573512906846239</v>
       </c>
-      <c r="U45" t="n">
+      <c r="W45" t="n">
         <v>0.06343508343508344</v>
       </c>
-      <c r="V45" t="n">
+      <c r="X45" t="n">
         <v>0.03316582914572865</v>
       </c>
-      <c r="W45" t="n">
+      <c r="Y45" t="n">
         <v>0.08935642251072358</v>
       </c>
-      <c r="X45" t="n">
+      <c r="Z45" t="n">
         <v>0.08399796455544208</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="AA45" t="n">
         <v>0.06570737884194774</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AB45" t="n">
         <v>0.1589719984656694</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AC45" t="n">
         <v>0.1084176059306007</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AD45" t="n">
         <v>0.07917241379310344</v>
       </c>
-      <c r="AC45" t="n">
+      <c r="AE45" t="n">
         <v>0.1198897204721268</v>
       </c>
-      <c r="AD45" t="n">
+      <c r="AF45" t="n">
         <v>0.06318407960199005</v>
       </c>
-      <c r="AE45" t="n">
+      <c r="AG45" t="n">
         <v>0.065</v>
       </c>
-      <c r="AF45" t="n">
+      <c r="AH45" t="n">
         <v>0.07122120817036071</v>
       </c>
-      <c r="AG45" t="n">
+      <c r="AI45" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5214,104 +5664,114 @@
       <c r="A46" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>346.978</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>342.552</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
         <v>100</v>
       </c>
-      <c r="C46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t xml:space="preserve"> As days went by, Martin noticed that he was thinking about Sophia less and less.</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>0.034</v>
       </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
         <v>0.06434653043848446</v>
       </c>
-      <c r="N46" t="n">
+      <c r="P46" t="n">
         <v>0.02054794520547945</v>
       </c>
-      <c r="O46" t="n">
+      <c r="Q46" t="n">
         <v>0.0671641791044776</v>
       </c>
-      <c r="P46" t="n">
+      <c r="R46" t="n">
         <v>0.0807057057057057</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="S46" t="n">
         <v>0.1040202966432475</v>
       </c>
-      <c r="R46" t="n">
+      <c r="T46" t="n">
         <v>0.5</v>
       </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
         <v>0.08823529411764706</v>
       </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
       <c r="W46" t="n">
         <v>0</v>
       </c>
       <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
         <v>0.06097560975609756</v>
       </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
         <v>0.08333333333333334</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AC46" t="n">
         <v>0.09745762711864407</v>
       </c>
-      <c r="AB46" t="n">
+      <c r="AD46" t="n">
         <v>0.1101190476190476</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AE46" t="n">
         <v>0.1911483253588517</v>
       </c>
-      <c r="AD46" t="n">
+      <c r="AF46" t="n">
         <v>0.1309523809523809</v>
       </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
         <v>0.0939982347749338</v>
       </c>
-      <c r="AG46" t="n">
+      <c r="AI46" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -5319,104 +5779,114 @@
       <c r="A47" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>355.692</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>347.419</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
         <v>82.5</v>
       </c>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="n">
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
         <v>17.5</v>
       </c>
-      <c r="E47" t="n">
+      <c r="G47" t="n">
         <v>59.65000000000001</v>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t xml:space="preserve">  He really felt prepared to see Sophia.  Martin called Sophia's cell and finally convinced her to come with him to the pub the next day.</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H47" t="n">
+      <c r="J47" t="n">
         <v>0.05710284805972926</v>
       </c>
-      <c r="I47" t="n">
+      <c r="K47" t="n">
         <v>0.04870785451376194</v>
       </c>
-      <c r="J47" t="n">
+      <c r="L47" t="n">
         <v>0.03068571565762577</v>
       </c>
-      <c r="K47" t="n">
+      <c r="M47" t="n">
         <v>0.04271813971549258</v>
       </c>
-      <c r="L47" t="n">
+      <c r="N47" t="n">
         <v>0.02320537735660048</v>
       </c>
-      <c r="M47" t="n">
+      <c r="O47" t="n">
         <v>0.06282657341499308</v>
       </c>
-      <c r="N47" t="n">
+      <c r="P47" t="n">
         <v>0.0455183966087513</v>
       </c>
-      <c r="O47" t="n">
+      <c r="Q47" t="n">
         <v>0.05393540274296853</v>
       </c>
-      <c r="P47" t="n">
+      <c r="R47" t="n">
         <v>0.03604672429997544</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="S47" t="n">
         <v>0.02659801266111625</v>
       </c>
-      <c r="R47" t="n">
+      <c r="T47" t="n">
         <v>2</v>
       </c>
-      <c r="S47" t="n">
+      <c r="U47" t="n">
         <v>0.1259868421052632</v>
       </c>
-      <c r="T47" t="n">
+      <c r="V47" t="n">
         <v>0.1039783001808318</v>
       </c>
-      <c r="U47" t="n">
+      <c r="W47" t="n">
         <v>0.1033972067896596</v>
       </c>
-      <c r="V47" t="n">
+      <c r="X47" t="n">
         <v>0.07274695592522724</v>
       </c>
-      <c r="W47" t="n">
+      <c r="Y47" t="n">
         <v>0.08561312085124381</v>
       </c>
-      <c r="X47" t="n">
+      <c r="Z47" t="n">
         <v>0.0627359819667512</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="AA47" t="n">
         <v>0.03220531887583643</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AB47" t="n">
         <v>0.06415397798097668</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="AC47" t="n">
         <v>0.05763664207813144</v>
       </c>
-      <c r="AB47" t="n">
+      <c r="AD47" t="n">
         <v>0.04613339588709047</v>
       </c>
-      <c r="AC47" t="n">
+      <c r="AE47" t="n">
         <v>0.07652421982127765</v>
       </c>
-      <c r="AD47" t="n">
+      <c r="AF47" t="n">
         <v>0.06372985666855616</v>
       </c>
-      <c r="AE47" t="n">
+      <c r="AG47" t="n">
         <v>0.02985965959988056</v>
       </c>
-      <c r="AF47" t="n">
+      <c r="AH47" t="n">
         <v>0.01601905857225006</v>
       </c>
-      <c r="AG47" t="n">
+      <c r="AI47" t="n">
         <v>1.4</v>
       </c>
     </row>
@@ -5424,67 +5894,71 @@
       <c r="A48" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>359.978</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>355.732</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
         <v>100</v>
       </c>
-      <c r="C48" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t xml:space="preserve"> When Martin arrived at the pub, Sophia was staring at the clock.</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H48" t="n">
+      <c r="J48" t="n">
         <v>0.1025641025641026</v>
       </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
         <v>0.08080808080808081</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
         <v>0.04285714285714286</v>
       </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
         <v>0.01470588235294117</v>
       </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
         <v>0.2</v>
       </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
       <c r="U48" t="n">
         <v>0</v>
       </c>
@@ -5492,36 +5966,42 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
         <v>0.06896551724137931</v>
       </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
       <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
         <v>0.125</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AC48" t="n">
         <v>0.2142857142857143</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AD48" t="n">
         <v>0.04</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AE48" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
       <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
         <v>0.07407407407407407</v>
       </c>
-      <c r="AG48" t="n">
+      <c r="AI48" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -5529,104 +6009,114 @@
       <c r="A49" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>365.86</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>361.055</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
         <v>86.5</v>
       </c>
-      <c r="C49" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" t="n">
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
         <v>13.5</v>
       </c>
-      <c r="E49" t="n">
+      <c r="G49" t="n">
         <v>29.24</v>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t xml:space="preserve">  How are you doing, Sophia?  he inquired, without losing control over his voice this once.</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H49" t="n">
+      <c r="J49" t="n">
         <v>0.03809523809523809</v>
       </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
         <v>0.04273504273504273</v>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
         <v>0.0597090449082859</v>
       </c>
-      <c r="M49" t="n">
+      <c r="O49" t="n">
         <v>0.09563375692407949</v>
       </c>
-      <c r="N49" t="n">
+      <c r="P49" t="n">
         <v>0.1164371006094076</v>
       </c>
-      <c r="O49" t="n">
+      <c r="Q49" t="n">
         <v>0.08141269098035135</v>
       </c>
-      <c r="P49" t="n">
+      <c r="R49" t="n">
         <v>0.128931969351168</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="S49" t="n">
         <v>0.05952380952380953</v>
       </c>
-      <c r="R49" t="n">
+      <c r="T49" t="n">
         <v>1.5</v>
       </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
       <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
         <v>0.08080808080808081</v>
       </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="n">
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="X49" t="n">
+      <c r="Z49" t="n">
         <v>0.0998565151107524</v>
       </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="n">
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
         <v>0.3542923402223586</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AC49" t="n">
         <v>0.203956072529271</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AD49" t="n">
         <v>0.07373737373737374</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AE49" t="n">
         <v>0.1352813852813853</v>
       </c>
-      <c r="AD49" t="n">
+      <c r="AF49" t="n">
         <v>0.1303680981595092</v>
       </c>
-      <c r="AE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="n">
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
         <v>0.1909424872026498</v>
       </c>
-      <c r="AG49" t="n">
+      <c r="AI49" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -5634,104 +6124,114 @@
       <c r="A50" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>374.91</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>367.322</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
         <v>63.6</v>
       </c>
-      <c r="C50" t="n">
+      <c r="E50" t="n">
         <v>11</v>
       </c>
-      <c r="D50" t="n">
+      <c r="F50" t="n">
         <v>25.4</v>
       </c>
-      <c r="E50" t="n">
+      <c r="G50" t="n">
         <v>47.67</v>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t xml:space="preserve">  I could be worse.  How are you these days?  Feeling better, he replied, actually believing that the response he made was true.</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H50" t="n">
+      <c r="J50" t="n">
         <v>0.03303433144037171</v>
       </c>
-      <c r="I50" t="n">
+      <c r="K50" t="n">
         <v>0.04993320206140889</v>
       </c>
-      <c r="J50" t="n">
+      <c r="L50" t="n">
         <v>0.03594390507011867</v>
       </c>
-      <c r="K50" t="n">
+      <c r="M50" t="n">
         <v>0.05994495835339159</v>
       </c>
-      <c r="L50" t="n">
+      <c r="N50" t="n">
         <v>0.06029645460025207</v>
       </c>
-      <c r="M50" t="n">
+      <c r="O50" t="n">
         <v>0.09625110521662247</v>
       </c>
-      <c r="N50" t="n">
+      <c r="P50" t="n">
         <v>0.03178506375227687</v>
       </c>
-      <c r="O50" t="n">
+      <c r="Q50" t="n">
         <v>0.05593073593073594</v>
       </c>
-      <c r="P50" t="n">
+      <c r="R50" t="n">
         <v>0.009909909909909909</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="S50" t="n">
         <v>0.03219616204690832</v>
       </c>
-      <c r="R50" t="n">
+      <c r="T50" t="n">
         <v>1.25</v>
       </c>
-      <c r="S50" t="n">
+      <c r="U50" t="n">
         <v>0.02403846153846154</v>
       </c>
-      <c r="T50" t="n">
+      <c r="V50" t="n">
         <v>0.03070175438596491</v>
       </c>
-      <c r="U50" t="n">
+      <c r="W50" t="n">
         <v>0.08572731418148655</v>
       </c>
-      <c r="V50" t="n">
+      <c r="X50" t="n">
         <v>0.06112409896746542</v>
       </c>
-      <c r="W50" t="n">
+      <c r="Y50" t="n">
         <v>0.1225283362290064</v>
       </c>
-      <c r="X50" t="n">
+      <c r="Z50" t="n">
         <v>0.02439024390243903</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="AA50" t="n">
         <v>0.07484802431610942</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AB50" t="n">
         <v>0.1748876495749635</v>
       </c>
-      <c r="AA50" t="n">
+      <c r="AC50" t="n">
         <v>0.1121295824126013</v>
       </c>
-      <c r="AB50" t="n">
+      <c r="AD50" t="n">
         <v>0.06717752234993615</v>
       </c>
-      <c r="AC50" t="n">
+      <c r="AE50" t="n">
         <v>0.06193806193806194</v>
       </c>
-      <c r="AD50" t="n">
+      <c r="AF50" t="n">
         <v>0.05487804878048781</v>
       </c>
-      <c r="AE50" t="n">
+      <c r="AG50" t="n">
         <v>0.0843497798972854</v>
       </c>
-      <c r="AF50" t="n">
+      <c r="AH50" t="n">
         <v>0.02792792792792793</v>
       </c>
-      <c r="AG50" t="n">
+      <c r="AI50" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -5739,88 +6239,92 @@
       <c r="A51" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>380.477</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>376.032</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
         <v>100</v>
       </c>
-      <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="inlineStr">
         <is>
           <t xml:space="preserve">  I have to go to the bathroom.  Do you need anything?  Sophia inquired quietly.</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H51" t="n">
+      <c r="J51" t="n">
         <v>0.03778184034125533</v>
       </c>
-      <c r="I51" t="n">
+      <c r="K51" t="n">
         <v>0.1176701057855557</v>
       </c>
-      <c r="J51" t="n">
+      <c r="L51" t="n">
         <v>0.03245942571785268</v>
       </c>
-      <c r="K51" t="n">
+      <c r="M51" t="n">
         <v>0.06343359934520156</v>
       </c>
-      <c r="L51" t="n">
+      <c r="N51" t="n">
         <v>0.02629848783694938</v>
       </c>
-      <c r="M51" t="n">
+      <c r="O51" t="n">
         <v>0.08393532851737186</v>
       </c>
-      <c r="N51" t="n">
+      <c r="P51" t="n">
         <v>0.04232804232804233</v>
       </c>
-      <c r="O51" t="n">
+      <c r="Q51" t="n">
         <v>0.08183183183183183</v>
       </c>
-      <c r="P51" t="n">
+      <c r="R51" t="n">
         <v>0.0136986301369863</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="S51" t="n">
         <v>0.06095238095238095</v>
       </c>
-      <c r="R51" t="n">
+      <c r="T51" t="n">
         <v>1.5</v>
       </c>
-      <c r="S51" t="n">
+      <c r="U51" t="n">
         <v>0.2483443708609271</v>
       </c>
-      <c r="T51" t="n">
+      <c r="V51" t="n">
         <v>0.1351351351351351</v>
       </c>
-      <c r="U51" t="n">
+      <c r="W51" t="n">
         <v>0.1491935483870968</v>
       </c>
-      <c r="V51" t="n">
+      <c r="X51" t="n">
         <v>0.1404682274247492</v>
       </c>
-      <c r="W51" t="n">
+      <c r="Y51" t="n">
         <v>0.1785714285714286</v>
       </c>
-      <c r="X51" t="n">
+      <c r="Z51" t="n">
         <v>0.1159420289855072</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="AA51" t="n">
         <v>0.08641975308641975</v>
       </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
       <c r="AB51" t="n">
         <v>0</v>
       </c>
@@ -5837,6 +6341,12 @@
         <v>0</v>
       </c>
       <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -5844,104 +6354,114 @@
       <c r="A52" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>385.122</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>380.517</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
         <v>73.59999999999999</v>
       </c>
-      <c r="C52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" t="n">
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
         <v>26.4</v>
       </c>
-      <c r="E52" t="n">
+      <c r="G52" t="n">
         <v>51.06</v>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t xml:space="preserve">  No, I'm fine.  I was just eager to discuss our former relationship, Martin replied.</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H52" t="n">
+      <c r="J52" t="n">
         <v>0.04006723053567555</v>
       </c>
-      <c r="I52" t="n">
+      <c r="K52" t="n">
         <v>0.06685932601880877</v>
       </c>
-      <c r="J52" t="n">
+      <c r="L52" t="n">
         <v>0.06287756745871929</v>
       </c>
-      <c r="K52" t="n">
+      <c r="M52" t="n">
         <v>0.02767857142857143</v>
       </c>
-      <c r="L52" t="n">
+      <c r="N52" t="n">
         <v>0.09554160324708269</v>
       </c>
-      <c r="M52" t="n">
+      <c r="O52" t="n">
         <v>0.05893567639257295</v>
       </c>
-      <c r="N52" t="n">
+      <c r="P52" t="n">
         <v>0.006944444444444444</v>
       </c>
-      <c r="O52" t="n">
+      <c r="Q52" t="n">
         <v>0.03840732910500352</v>
       </c>
-      <c r="P52" t="n">
+      <c r="R52" t="n">
         <v>0.03312155470428852</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="S52" t="n">
         <v>0.01293103448275862</v>
       </c>
-      <c r="R52" t="n">
+      <c r="T52" t="n">
         <v>2</v>
       </c>
-      <c r="S52" t="n">
+      <c r="U52" t="n">
         <v>0.1861159558162888</v>
       </c>
-      <c r="T52" t="n">
+      <c r="V52" t="n">
         <v>0.3012566137566138</v>
       </c>
-      <c r="U52" t="n">
+      <c r="W52" t="n">
         <v>0.1259042033235581</v>
       </c>
-      <c r="V52" t="n">
+      <c r="X52" t="n">
         <v>0.07352941176470588</v>
       </c>
-      <c r="W52" t="n">
+      <c r="Y52" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="X52" t="n">
+      <c r="Z52" t="n">
         <v>0.1717479674796748</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="AA52" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0</v>
-      </c>
       <c r="AB52" t="n">
         <v>0</v>
       </c>
       <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
         <v>0.03508771929824561</v>
       </c>
-      <c r="AD52" t="n">
+      <c r="AF52" t="n">
         <v>0.02898550724637681</v>
       </c>
-      <c r="AE52" t="n">
+      <c r="AG52" t="n">
         <v>0.07843137254901961</v>
       </c>
-      <c r="AF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="n">
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5949,88 +6469,92 @@
       <c r="A53" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>388.986</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>385.162</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
         <v>86.7</v>
       </c>
-      <c r="C53" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" t="n">
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
         <v>13.3</v>
       </c>
-      <c r="E53" t="n">
+      <c r="G53" t="n">
         <v>25</v>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t xml:space="preserve"> By the way, do you have a Kit Kat on you by any chance?</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H53" t="n">
+      <c r="J53" t="n">
         <v>0.0708955223880597</v>
       </c>
-      <c r="I53" t="n">
+      <c r="K53" t="n">
         <v>0.05405405405405406</v>
       </c>
-      <c r="J53" t="n">
+      <c r="L53" t="n">
         <v>0.04347826086956521</v>
       </c>
-      <c r="K53" t="n">
+      <c r="M53" t="n">
         <v>0.02631578947368421</v>
       </c>
-      <c r="L53" t="n">
+      <c r="N53" t="n">
         <v>0.05</v>
       </c>
-      <c r="M53" t="n">
+      <c r="O53" t="n">
         <v>0.049079754601227</v>
       </c>
-      <c r="N53" t="n">
+      <c r="P53" t="n">
         <v>0.060849598163031</v>
       </c>
-      <c r="O53" t="n">
+      <c r="Q53" t="n">
         <v>0.04221491228070175</v>
       </c>
-      <c r="P53" t="n">
+      <c r="R53" t="n">
         <v>0.03282275711159737</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="S53" t="n">
         <v>0.05606860158311346</v>
       </c>
-      <c r="R53" t="n">
+      <c r="T53" t="n">
         <v>1</v>
       </c>
-      <c r="S53" t="n">
+      <c r="U53" t="n">
         <v>0.1506578947368421</v>
       </c>
-      <c r="T53" t="n">
+      <c r="V53" t="n">
         <v>0.2256747670732879</v>
       </c>
-      <c r="U53" t="n">
+      <c r="W53" t="n">
         <v>0.2017670393076091</v>
       </c>
-      <c r="V53" t="n">
+      <c r="X53" t="n">
         <v>0.1200249092976661</v>
       </c>
-      <c r="W53" t="n">
+      <c r="Y53" t="n">
         <v>0.1572479764532745</v>
       </c>
-      <c r="X53" t="n">
+      <c r="Z53" t="n">
         <v>0.1550760523523169</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="AA53" t="n">
         <v>0.04411764705882353</v>
       </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0</v>
-      </c>
       <c r="AB53" t="n">
         <v>0</v>
       </c>
@@ -6044,9 +6568,15 @@
         <v>0</v>
       </c>
       <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
         <v>0.0509433962264151</v>
       </c>
-      <c r="AG53" t="n">
+      <c r="AI53" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6054,40 +6584,44 @@
       <c r="A54" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>393.919</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>389.692</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
         <v>100</v>
       </c>
-      <c r="C54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t xml:space="preserve">  What?  No, Sophia answered, looking at Martin sympathetically.</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H54" t="n">
+      <c r="J54" t="n">
         <v>0.07943925233644859</v>
       </c>
-      <c r="I54" t="n">
+      <c r="K54" t="n">
         <v>0.102880658436214</v>
       </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
@@ -6098,60 +6632,66 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
         <v>0.09787234042553193</v>
       </c>
-      <c r="P54" t="n">
+      <c r="R54" t="n">
         <v>0.07531380753138077</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="S54" t="n">
         <v>0.065</v>
       </c>
-      <c r="R54" t="n">
+      <c r="T54" t="n">
         <v>0.25</v>
       </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
       <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
         <v>0.125</v>
       </c>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0</v>
-      </c>
       <c r="X54" t="n">
         <v>0</v>
       </c>
       <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
         <v>0.09230769230769231</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="AB54" t="n">
         <v>0.1538461538461539</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="AC54" t="n">
         <v>0.1443298969072165</v>
       </c>
-      <c r="AB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" t="n">
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
         <v>0.1573033707865168</v>
       </c>
-      <c r="AD54" t="n">
+      <c r="AF54" t="n">
         <v>0.140625</v>
       </c>
-      <c r="AE54" t="n">
+      <c r="AG54" t="n">
         <v>0.1384615384615385</v>
       </c>
-      <c r="AF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="n">
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -6159,104 +6699,114 @@
       <c r="A55" s="1" t="n">
         <v>53</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>402.434</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>394.7</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
         <v>83.3</v>
       </c>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="n">
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
         <v>16.7</v>
       </c>
-      <c r="E55" t="n">
+      <c r="G55" t="n">
         <v>52.66999999999999</v>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t xml:space="preserve">  Martin felt like a new person.  That's okay.  I'll be back in a jiffy, Martin said while he jumped to find a nearby kiosk.</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H55" t="n">
+      <c r="J55" t="n">
         <v>0.001629072681704261</v>
       </c>
-      <c r="I55" t="n">
+      <c r="K55" t="n">
         <v>0.03856066791083074</v>
       </c>
-      <c r="J55" t="n">
+      <c r="L55" t="n">
         <v>0.01957251377705796</v>
       </c>
-      <c r="K55" t="n">
+      <c r="M55" t="n">
         <v>0.01951363893805991</v>
       </c>
-      <c r="L55" t="n">
+      <c r="N55" t="n">
         <v>0.007804638318784957</v>
       </c>
-      <c r="M55" t="n">
+      <c r="O55" t="n">
         <v>0.07895825427337193</v>
       </c>
-      <c r="N55" t="n">
+      <c r="P55" t="n">
         <v>0.03134717871629741</v>
       </c>
-      <c r="O55" t="n">
+      <c r="Q55" t="n">
         <v>0.04871088997402256</v>
       </c>
-      <c r="P55" t="n">
+      <c r="R55" t="n">
         <v>0.02966176696753833</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="S55" t="n">
         <v>0.05620792771902789</v>
       </c>
-      <c r="R55" t="n">
+      <c r="T55" t="n">
         <v>1</v>
       </c>
-      <c r="S55" t="n">
+      <c r="U55" t="n">
         <v>0.08857023473877568</v>
       </c>
-      <c r="T55" t="n">
+      <c r="V55" t="n">
         <v>0.11510320937324</v>
       </c>
-      <c r="U55" t="n">
+      <c r="W55" t="n">
         <v>0.01590693257359924</v>
       </c>
-      <c r="V55" t="n">
+      <c r="X55" t="n">
         <v>0.01584694947538451</v>
       </c>
-      <c r="W55" t="n">
+      <c r="Y55" t="n">
         <v>0.04959433865924778</v>
       </c>
-      <c r="X55" t="n">
+      <c r="Z55" t="n">
         <v>0.03533212194629518</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="AA55" t="n">
         <v>0.01193351736829998</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="AB55" t="n">
         <v>0.0370950983557404</v>
       </c>
-      <c r="AA55" t="n">
+      <c r="AC55" t="n">
         <v>0.02513821860362301</v>
       </c>
-      <c r="AB55" t="n">
+      <c r="AD55" t="n">
         <v>0.06673490233171868</v>
       </c>
-      <c r="AC55" t="n">
+      <c r="AE55" t="n">
         <v>0.06461843919970976</v>
       </c>
-      <c r="AD55" t="n">
+      <c r="AF55" t="n">
         <v>0.06305491763023535</v>
       </c>
-      <c r="AE55" t="n">
+      <c r="AG55" t="n">
         <v>0.02377697677181433</v>
       </c>
-      <c r="AF55" t="n">
+      <c r="AH55" t="n">
         <v>0.03857091029375673</v>
       </c>
-      <c r="AG55" t="n">
+      <c r="AI55" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6264,104 +6814,114 @@
       <c r="A56" s="1" t="n">
         <v>54</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>407.502</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>402.454</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
         <v>85.7</v>
       </c>
-      <c r="C56" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="n">
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
         <v>14.3</v>
       </c>
-      <c r="E56" t="n">
+      <c r="G56" t="n">
         <v>45.88</v>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t xml:space="preserve"> On the way to their table, while munching what was left of the Kit Kat, Martin laughed at himself.</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
         <v>0.03030303030303031</v>
       </c>
-      <c r="J56" t="n">
+      <c r="L56" t="n">
         <v>0.02150537634408602</v>
       </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
         <v>0.05314009661835748</v>
       </c>
-      <c r="M56" t="n">
+      <c r="O56" t="n">
         <v>0.09830469103232579</v>
       </c>
-      <c r="N56" t="n">
+      <c r="P56" t="n">
         <v>0.08129790334725757</v>
       </c>
-      <c r="O56" t="n">
+      <c r="Q56" t="n">
         <v>0.06551932367149758</v>
       </c>
-      <c r="P56" t="n">
+      <c r="R56" t="n">
         <v>0.1151815296920041</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="S56" t="n">
         <v>0.06681876382843842</v>
       </c>
-      <c r="R56" t="n">
+      <c r="T56" t="n">
         <v>0.6</v>
       </c>
-      <c r="S56" t="n">
+      <c r="U56" t="n">
         <v>0.05043859649122807</v>
       </c>
-      <c r="T56" t="n">
+      <c r="V56" t="n">
         <v>0.1173193511387842</v>
       </c>
-      <c r="U56" t="n">
+      <c r="W56" t="n">
         <v>0.05649717514124294</v>
       </c>
-      <c r="V56" t="n">
+      <c r="X56" t="n">
         <v>0.09567028211337443</v>
       </c>
-      <c r="W56" t="n">
+      <c r="Y56" t="n">
         <v>0.05298013245033113</v>
       </c>
-      <c r="X56" t="n">
+      <c r="Z56" t="n">
         <v>0.1215658530833628</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="AA56" t="n">
         <v>0.05</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="AB56" t="n">
         <v>0.2397372742200329</v>
       </c>
-      <c r="AA56" t="n">
+      <c r="AC56" t="n">
         <v>0.07370184254606366</v>
       </c>
-      <c r="AB56" t="n">
+      <c r="AD56" t="n">
         <v>0.1454022988505747</v>
       </c>
-      <c r="AC56" t="n">
+      <c r="AE56" t="n">
         <v>0.125</v>
       </c>
-      <c r="AD56" t="n">
+      <c r="AF56" t="n">
         <v>0.09742457689477557</v>
       </c>
-      <c r="AE56" t="n">
+      <c r="AG56" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="AF56" t="n">
+      <c r="AH56" t="n">
         <v>0.08230832013058716</v>
       </c>
-      <c r="AG56" t="n">
+      <c r="AI56" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -6369,67 +6929,71 @@
       <c r="A57" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>413.893</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>408.023</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="C57" t="n">
+      <c r="E57" t="n">
         <v>9.6</v>
       </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
         <v>-15.11</v>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t xml:space="preserve">  Why didn't I go to Andre the Giant sooner?  I must never admit this to Mom.</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H57" t="n">
+      <c r="J57" t="n">
         <v>0.03472222222222222</v>
       </c>
-      <c r="I57" t="n">
+      <c r="K57" t="n">
         <v>0.06060606060606061</v>
       </c>
-      <c r="J57" t="n">
+      <c r="L57" t="n">
         <v>0.07246376811594203</v>
       </c>
-      <c r="K57" t="n">
+      <c r="M57" t="n">
         <v>0.01333333333333333</v>
       </c>
-      <c r="L57" t="n">
+      <c r="N57" t="n">
         <v>0.02564102564102564</v>
       </c>
-      <c r="M57" t="n">
+      <c r="O57" t="n">
         <v>0.02150537634408602</v>
       </c>
-      <c r="N57" t="n">
+      <c r="P57" t="n">
         <v>0.0617283950617284</v>
       </c>
-      <c r="O57" t="n">
+      <c r="Q57" t="n">
         <v>0.05491525423728814</v>
       </c>
-      <c r="P57" t="n">
+      <c r="R57" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="S57" t="n">
         <v>0.06613756613756613</v>
       </c>
-      <c r="R57" t="n">
+      <c r="T57" t="n">
         <v>1.5</v>
       </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
       <c r="U57" t="n">
         <v>0</v>
       </c>
@@ -6467,6 +7031,12 @@
         <v>0</v>
       </c>
       <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="n">
         <v>0</v>
       </c>
     </row>
